--- a/Notes and data for listed articles/(row 3) data for 2023 Chen et al./raw_data/data_for_escape_latency.xlsx
+++ b/Notes and data for listed articles/(row 3) data for 2023 Chen et al./raw_data/data_for_escape_latency.xlsx
@@ -161,7 +161,7 @@
     <xdr:ext cx="3981450" cy="2524125"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -217,7 +217,7 @@
     <xdr:ext cx="3676650" cy="2295525"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>

--- a/Notes and data for listed articles/(row 3) data for 2023 Chen et al./raw_data/data_for_escape_latency.xlsx
+++ b/Notes and data for listed articles/(row 3) data for 2023 Chen et al./raw_data/data_for_escape_latency.xlsx
@@ -133,7 +133,7 @@
     <xdr:ext cx="3400425" cy="2524125"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image3.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -189,7 +189,7 @@
     <xdr:ext cx="3200400" cy="2295525"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image4.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
